--- a/GRADO_CLAUDE.xlsx
+++ b/GRADO_CLAUDE.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="527">
   <si>
     <t>id_titulo</t>
   </si>
@@ -176,12 +176,18 @@
     <t>Vizconde de Villena</t>
   </si>
   <si>
+    <t>Vizcondado de Villena</t>
+  </si>
+  <si>
     <t>TIT0012</t>
   </si>
   <si>
     <t>Vizconde de Buen Viaje</t>
   </si>
   <si>
+    <t>Vizcondado de Buen Viaje</t>
+  </si>
+  <si>
     <t>TIT0013</t>
   </si>
   <si>
@@ -1268,6 +1274,30 @@
     <t>Secretaría de Guerra y Hacienda</t>
   </si>
   <si>
+    <t>JEF047</t>
+  </si>
+  <si>
+    <t>Comandancia de Marina de Río de la Plata</t>
+  </si>
+  <si>
+    <t>JEF048</t>
+  </si>
+  <si>
+    <t>Apostadero de Montevideo</t>
+  </si>
+  <si>
+    <t>JEF049</t>
+  </si>
+  <si>
+    <t>Comandancia de Marina del Mar del Sur</t>
+  </si>
+  <si>
+    <t>JEF050</t>
+  </si>
+  <si>
+    <t>Apostadero de Lima</t>
+  </si>
+  <si>
     <t>id_rama</t>
   </si>
   <si>
@@ -1491,6 +1521,21 @@
   </si>
   <si>
     <t>BUQ00074</t>
+  </si>
+  <si>
+    <t>ESC0006</t>
+  </si>
+  <si>
+    <t>Escuadra José de Córdova y Ramos</t>
+  </si>
+  <si>
+    <t>BUQ00046</t>
+  </si>
+  <si>
+    <t>Escuadra de convoy de vuelta a España con caudales</t>
+  </si>
+  <si>
+    <t>25/2/1785</t>
   </si>
   <si>
     <t>id_reales_ejercitos</t>
@@ -1560,10 +1605,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1591,6 +1637,11 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1621,7 +1672,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1656,6 +1707,9 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2129,7 +2183,7 @@
         <v>51</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
@@ -2141,13 +2195,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
@@ -2159,10 +2213,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>13</v>
@@ -2177,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>40</v>
@@ -2190,15 +2244,15 @@
         <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
@@ -2208,15 +2262,15 @@
         <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
@@ -2226,18 +2280,18 @@
         <v>8</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
@@ -2249,13 +2303,13 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
@@ -2267,17 +2321,17 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -2285,10 +2339,10 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
@@ -2298,15 +2352,15 @@
         <v>8</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>18</v>
@@ -2321,10 +2375,10 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>18</v>
@@ -2339,10 +2393,10 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>18</v>
@@ -2357,10 +2411,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>18</v>
@@ -2375,13 +2429,13 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
@@ -2393,10 +2447,10 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>18</v>
@@ -2411,10 +2465,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>18</v>
@@ -2429,13 +2483,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
@@ -2447,16 +2501,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>19</v>
@@ -2467,16 +2521,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>19</v>
@@ -2487,16 +2541,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>19</v>
@@ -2507,13 +2561,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D33" s="2">
         <v>1520.0</v>
@@ -2522,7 +2576,7 @@
         <v>44</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2543,200 +2597,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2" s="7">
         <v>1.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C3" s="7">
         <v>2.0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" s="7">
         <v>3.0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E4" s="5"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" s="7">
         <v>4.0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C6" s="7">
         <v>5.0</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C7" s="7">
         <v>6.0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C8" s="7">
         <v>7.0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E8" s="5"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7">
         <v>8.0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" s="7">
         <v>9.0</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C11" s="7">
         <v>10.0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C12" s="7">
         <v>11.0</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C13" s="7">
         <v>12.0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E13" s="5"/>
     </row>
@@ -2773,572 +2827,572 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3358,21 +3412,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C2" s="9">
         <v>1.0</v>
@@ -3380,10 +3434,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C3" s="9">
         <v>2.0</v>
@@ -3391,10 +3445,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C4" s="9">
         <v>3.0</v>
@@ -3402,10 +3456,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C5" s="9">
         <v>4.0</v>
@@ -3413,10 +3467,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C6" s="9">
         <v>5.0</v>
@@ -3424,10 +3478,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C7" s="9">
         <v>6.0</v>
@@ -3435,10 +3489,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C8" s="9">
         <v>7.0</v>
@@ -3446,10 +3500,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C9" s="9">
         <v>8.0</v>
@@ -3457,10 +3511,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C10" s="9">
         <v>9.0</v>
@@ -3468,10 +3522,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C11" s="9">
         <v>10.0</v>
@@ -3479,10 +3533,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C12" s="9">
         <v>11.0</v>
@@ -3490,10 +3544,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C13" s="9">
         <v>12.0</v>
@@ -3501,10 +3555,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C14" s="9">
         <v>13.0</v>
@@ -3512,10 +3566,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C15" s="9">
         <v>14.0</v>
@@ -3542,567 +3596,605 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>321</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="D23" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>372</v>
-      </c>
       <c r="D27" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>396</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>401</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -4122,76 +4214,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>44</v>
@@ -4199,109 +4291,109 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -4325,113 +4417,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>471</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>489</v>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -4452,119 +4561,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/GRADO_CLAUDE.xlsx
+++ b/GRADO_CLAUDE.xlsx
@@ -8,9 +8,11 @@
     <sheet state="visible" name="Funcion" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Funcion Tripulacion Buque" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="Jefatura" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="Rama" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Escuadra" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="REALES EJERCITOS" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Comision" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="Rama" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="Escuadra" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="Division" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="REALES EJERCITOS" sheetId="10" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -18,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="599">
   <si>
     <t>id_titulo</t>
   </si>
@@ -281,12 +283,18 @@
     <t>Marquesado de la Victoria</t>
   </si>
   <si>
+    <t>24/03/1744</t>
+  </si>
+  <si>
     <t>TIT0026</t>
   </si>
   <si>
     <t>Vizconde de Viana</t>
   </si>
   <si>
+    <t>Vizcondado de Viana</t>
+  </si>
+  <si>
     <t>TIT0027</t>
   </si>
   <si>
@@ -347,6 +355,27 @@
     <t>Grandeza de España</t>
   </si>
   <si>
+    <t>TIT0033</t>
+  </si>
+  <si>
+    <t>Masqués de Matallana</t>
+  </si>
+  <si>
+    <t>Masquesado de Matallana</t>
+  </si>
+  <si>
+    <t>31/08/1745</t>
+  </si>
+  <si>
+    <t>TIT0034</t>
+  </si>
+  <si>
+    <t>Caballero de la Orden de San Genaro</t>
+  </si>
+  <si>
+    <t>Real Orden de San Genaro</t>
+  </si>
+  <si>
     <t>id_grado</t>
   </si>
   <si>
@@ -869,6 +898,30 @@
     <t>Intendente de Marina</t>
   </si>
   <si>
+    <t>FUNC069</t>
+  </si>
+  <si>
+    <t>Oficial de Órdenes</t>
+  </si>
+  <si>
+    <t>FUNC070</t>
+  </si>
+  <si>
+    <t>Presbítero</t>
+  </si>
+  <si>
+    <t>FUNC071</t>
+  </si>
+  <si>
+    <t>Teniente de Infantería</t>
+  </si>
+  <si>
+    <t>FUNC072</t>
+  </si>
+  <si>
+    <t>Obispo</t>
+  </si>
+  <si>
     <t>id_funcion_buque</t>
   </si>
   <si>
@@ -1289,7 +1342,7 @@
     <t>JEF049</t>
   </si>
   <si>
-    <t>Comandancia de Marina del Mar del Sur</t>
+    <t>Comandancia de Marina de Lima</t>
   </si>
   <si>
     <t>JEF050</t>
@@ -1298,6 +1351,75 @@
     <t>Apostadero de Lima</t>
   </si>
   <si>
+    <t>JEF051</t>
+  </si>
+  <si>
+    <t>Corona francesa</t>
+  </si>
+  <si>
+    <t>JEF052</t>
+  </si>
+  <si>
+    <t>Obispado de Cuzco</t>
+  </si>
+  <si>
+    <t>JEF053</t>
+  </si>
+  <si>
+    <t>Dirección General de Rentas de Correos</t>
+  </si>
+  <si>
+    <t>JEF054</t>
+  </si>
+  <si>
+    <t>Renta de Correos de Lima</t>
+  </si>
+  <si>
+    <t>JEF055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Adminsitración de Temporalidades </t>
+  </si>
+  <si>
+    <t>JEF056</t>
+  </si>
+  <si>
+    <t>Junta de Temporalidades de Lima</t>
+  </si>
+  <si>
+    <t>id_comision</t>
+  </si>
+  <si>
+    <t>nombre_comision</t>
+  </si>
+  <si>
+    <t>fecha_inicio</t>
+  </si>
+  <si>
+    <t>fecha_fin</t>
+  </si>
+  <si>
+    <t>id_jefatura_orden</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>COMI0000001</t>
+  </si>
+  <si>
+    <t>Conducción de azogues a Nueva España</t>
+  </si>
+  <si>
+    <t>15/02/1788</t>
+  </si>
+  <si>
+    <t>01/05/1788</t>
+  </si>
+  <si>
+    <t>Real orden para transporte con destino final Veracruz</t>
+  </si>
+  <si>
     <t>id_rama</t>
   </si>
   <si>
@@ -1454,9 +1576,6 @@
     <t>fecha_disolucion</t>
   </si>
   <si>
-    <t>descripcion</t>
-  </si>
-  <si>
     <t>ESC0001</t>
   </si>
   <si>
@@ -1536,6 +1655,105 @@
   </si>
   <si>
     <t>25/2/1785</t>
+  </si>
+  <si>
+    <t>ESC0007</t>
+  </si>
+  <si>
+    <t>Escuadra expedicionaria contra Argel</t>
+  </si>
+  <si>
+    <t>BUQ00104</t>
+  </si>
+  <si>
+    <t>20/05/1775</t>
+  </si>
+  <si>
+    <t>20/07/1775</t>
+  </si>
+  <si>
+    <t>Retirada de Argel. Fracaso en el desembarco</t>
+  </si>
+  <si>
+    <t>id_division</t>
+  </si>
+  <si>
+    <t>nombre_division</t>
+  </si>
+  <si>
+    <t>id_jefe_division</t>
+  </si>
+  <si>
+    <t>DIVI00000001</t>
+  </si>
+  <si>
+    <t>1ª División</t>
+  </si>
+  <si>
+    <t>24/05/1775</t>
+  </si>
+  <si>
+    <t>DIVI00000002</t>
+  </si>
+  <si>
+    <t>2ª División</t>
+  </si>
+  <si>
+    <t>BUQ00106</t>
+  </si>
+  <si>
+    <t>DIVI00000003</t>
+  </si>
+  <si>
+    <t>3ª División</t>
+  </si>
+  <si>
+    <t>DIVI00000004</t>
+  </si>
+  <si>
+    <t>4ª División</t>
+  </si>
+  <si>
+    <t>DIVI00000005</t>
+  </si>
+  <si>
+    <t>5ª División</t>
+  </si>
+  <si>
+    <t>DIVI00000006</t>
+  </si>
+  <si>
+    <t>6ª División</t>
+  </si>
+  <si>
+    <t>DIVI00000007</t>
+  </si>
+  <si>
+    <t>7ª División</t>
+  </si>
+  <si>
+    <t>DIVI00000008</t>
+  </si>
+  <si>
+    <t>8ª División</t>
+  </si>
+  <si>
+    <t>DIVI00000009</t>
+  </si>
+  <si>
+    <t>1º Cuerpo de Batidores</t>
+  </si>
+  <si>
+    <t>BUQ00122</t>
+  </si>
+  <si>
+    <t>PER00090</t>
+  </si>
+  <si>
+    <t>DIVI00000010</t>
+  </si>
+  <si>
+    <t>2º Cuerpo de Batidores</t>
   </si>
   <si>
     <t>id_reales_ejercitos</t>
@@ -1723,6 +1941,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -1748,6 +1970,10 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -2437,7 +2663,9 @@
       <c r="C26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>19</v>
       </c>
@@ -2447,15 +2675,17 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
         <v>19</v>
       </c>
@@ -2465,10 +2695,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>18</v>
@@ -2483,13 +2713,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
@@ -2501,16 +2731,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>19</v>
@@ -2521,16 +2751,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>19</v>
@@ -2541,16 +2771,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>19</v>
@@ -2561,13 +2791,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D33" s="2">
         <v>1520.0</v>
@@ -2576,7 +2806,177 @@
         <v>44</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="2" width="17.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -2597,200 +2997,200 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C2" s="7">
         <v>1.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C3" s="7">
         <v>2.0</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E3" s="5"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C4" s="7">
         <v>3.0</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E4" s="5"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C5" s="7">
         <v>4.0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C6" s="7">
         <v>5.0</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C7" s="7">
         <v>6.0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E7" s="5"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C8" s="7">
         <v>7.0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E8" s="5"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C9" s="7">
         <v>8.0</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C10" s="7">
         <v>9.0</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E10" s="5"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C11" s="7">
         <v>10.0</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C12" s="7">
         <v>11.0</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C13" s="7">
         <v>12.0</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E13" s="5"/>
     </row>
@@ -2827,572 +3227,604 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>282</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -3412,21 +3844,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C2" s="9">
         <v>1.0</v>
@@ -3434,10 +3866,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C3" s="9">
         <v>2.0</v>
@@ -3445,10 +3877,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C4" s="9">
         <v>3.0</v>
@@ -3456,10 +3888,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C5" s="9">
         <v>4.0</v>
@@ -3467,10 +3899,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C6" s="9">
         <v>5.0</v>
@@ -3478,10 +3910,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="C7" s="9">
         <v>6.0</v>
@@ -3489,10 +3921,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C8" s="9">
         <v>7.0</v>
@@ -3500,10 +3932,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C9" s="9">
         <v>8.0</v>
@@ -3511,10 +3943,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="C10" s="9">
         <v>9.0</v>
@@ -3522,10 +3954,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C11" s="9">
         <v>10.0</v>
@@ -3533,10 +3965,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C12" s="9">
         <v>11.0</v>
@@ -3544,10 +3976,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C13" s="9">
         <v>12.0</v>
@@ -3555,10 +3987,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="C14" s="9">
         <v>13.0</v>
@@ -3566,10 +3998,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C15" s="9">
         <v>14.0</v>
@@ -3596,605 +4028,659 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>425</v>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -4209,191 +4695,48 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.25"/>
+    <col customWidth="1" min="2" max="2" width="33.0"/>
+    <col customWidth="1" min="5" max="5" width="17.13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>426</v>
+        <v>455</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>428</v>
+        <v>457</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C13" s="2" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>465</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -4402,6 +4745,205 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="15.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4417,130 +4959,153 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>513</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>514</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>475</v>
+        <v>515</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>476</v>
+        <v>516</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>477</v>
+        <v>517</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>479</v>
+        <v>518</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>485</v>
+        <v>524</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>491</v>
+        <v>530</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>494</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>497</v>
+        <v>536</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>496</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>498</v>
+        <v>537</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>499</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>505</v>
+        <v>544</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -4548,132 +5113,190 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.88"/>
-    <col customWidth="1" min="2" max="2" width="17.63"/>
+    <col customWidth="1" min="3" max="3" width="15.38"/>
+    <col customWidth="1" min="4" max="4" width="16.13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>508</v>
+        <v>552</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>426</v>
+        <v>515</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>509</v>
+        <v>554</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>432</v>
+        <v>547</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>512</v>
+        <v>557</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>511</v>
+        <v>558</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>432</v>
+        <v>559</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>514</v>
+        <v>560</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>432</v>
+        <v>561</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>516</v>
+        <v>562</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>432</v>
+        <v>563</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>518</v>
+        <v>564</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>429</v>
+        <v>545</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>520</v>
+        <v>566</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>429</v>
+        <v>545</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>429</v>
+        <v>545</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>524</v>
+        <v>570</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>432</v>
+        <v>571</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/GRADO_CLAUDE.xlsx
+++ b/GRADO_CLAUDE.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="616">
   <si>
     <t>id_titulo</t>
   </si>
@@ -922,6 +922,18 @@
     <t>Obispo</t>
   </si>
   <si>
+    <t>FUNC073</t>
+  </si>
+  <si>
+    <t>Embajador marroquí</t>
+  </si>
+  <si>
+    <t>FUNC074</t>
+  </si>
+  <si>
+    <t>Príncipe marroquí</t>
+  </si>
+  <si>
     <t>id_funcion_buque</t>
   </si>
   <si>
@@ -1570,6 +1582,9 @@
     <t>id_buque_insignia</t>
   </si>
   <si>
+    <t>id_nacion</t>
+  </si>
+  <si>
     <t>fecha_constitucion</t>
   </si>
   <si>
@@ -1588,6 +1603,9 @@
     <t>Escuadra de Operaciones</t>
   </si>
   <si>
+    <t>NACI00001</t>
+  </si>
+  <si>
     <t>01/08/1776</t>
   </si>
   <si>
@@ -1675,6 +1693,36 @@
     <t>Retirada de Argel. Fracaso en el desembarco</t>
   </si>
   <si>
+    <t>ESC0008</t>
+  </si>
+  <si>
+    <t>Escuadra de patrulla García del Postigo</t>
+  </si>
+  <si>
+    <t>BUQ00140</t>
+  </si>
+  <si>
+    <t>Escuadra de patrulla contra el corso argelino</t>
+  </si>
+  <si>
+    <t>ESC0009</t>
+  </si>
+  <si>
+    <t>Escuadra corsarios argelinos Mahamed Rais</t>
+  </si>
+  <si>
+    <t>BUQ00143</t>
+  </si>
+  <si>
+    <t>Escuadra de corso argelina</t>
+  </si>
+  <si>
+    <t>NACI00004</t>
+  </si>
+  <si>
+    <t>08/06/1758</t>
+  </si>
+  <si>
     <t>id_division</t>
   </si>
   <si>
@@ -1688,6 +1736,9 @@
   </si>
   <si>
     <t>1ª División</t>
+  </si>
+  <si>
+    <t>PER00082</t>
   </si>
   <si>
     <t>24/05/1775</t>
@@ -2864,119 +2915,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -3827,6 +3878,22 @@
         <v>299</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3844,10 +3911,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>120</v>
@@ -3855,10 +3922,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C2" s="9">
         <v>1.0</v>
@@ -3866,10 +3933,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C3" s="9">
         <v>2.0</v>
@@ -3877,10 +3944,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C4" s="9">
         <v>3.0</v>
@@ -3888,10 +3955,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C5" s="9">
         <v>4.0</v>
@@ -3899,7 +3966,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>124</v>
@@ -3910,10 +3977,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C7" s="9">
         <v>6.0</v>
@@ -3921,10 +3988,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C8" s="9">
         <v>7.0</v>
@@ -3932,10 +3999,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C9" s="9">
         <v>8.0</v>
@@ -3943,10 +4010,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C10" s="9">
         <v>9.0</v>
@@ -3954,10 +4021,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C11" s="9">
         <v>10.0</v>
@@ -3965,10 +4032,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C12" s="9">
         <v>11.0</v>
@@ -3976,10 +4043,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C13" s="9">
         <v>12.0</v>
@@ -3987,10 +4054,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C14" s="9">
         <v>13.0</v>
@@ -3998,10 +4065,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C15" s="9">
         <v>14.0</v>
@@ -4028,659 +4095,659 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="10" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>388</v>
-      </c>
       <c r="D26" s="11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="D38" s="11" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="D40" s="12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -4701,42 +4768,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -4756,76 +4823,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>44</v>
@@ -4833,109 +4900,109 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -4953,159 +5020,220 @@
     <col customWidth="1" min="2" max="2" width="30.38"/>
     <col customWidth="1" min="3" max="3" width="16.25"/>
     <col customWidth="1" min="4" max="4" width="31.0"/>
-    <col customWidth="1" min="5" max="5" width="16.0"/>
-    <col customWidth="1" min="6" max="6" width="18.75"/>
+    <col customWidth="1" min="5" max="6" width="16.0"/>
+    <col customWidth="1" min="7" max="7" width="18.75"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>460</v>
+        <v>522</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>522</v>
+        <v>526</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>523</v>
+        <v>528</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>527</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>528</v>
+        <v>533</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>532</v>
+        <v>537</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>533</v>
+        <v>538</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>544</v>
+        <v>549</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>527</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -5126,177 +5254,180 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>572</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>

--- a/GRADO_CLAUDE.xlsx
+++ b/GRADO_CLAUDE.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="623">
   <si>
     <t>id_titulo</t>
   </si>
@@ -1721,6 +1721,27 @@
   </si>
   <si>
     <t>08/06/1758</t>
+  </si>
+  <si>
+    <t>Escuadra destruida en combate</t>
+  </si>
+  <si>
+    <t>ESC0010</t>
+  </si>
+  <si>
+    <t>Escuadra de bombardeo contra Argel</t>
+  </si>
+  <si>
+    <t>BUQ00145</t>
+  </si>
+  <si>
+    <t>10/06/1783</t>
+  </si>
+  <si>
+    <t>26/09/1783</t>
+  </si>
+  <si>
+    <t>Bombardeo de castigo contra el corso argelino</t>
   </si>
   <si>
     <t>id_division</t>
@@ -2915,13 +2936,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>470</v>
@@ -2929,13 +2950,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>476</v>
@@ -2943,13 +2964,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>476</v>
@@ -2957,13 +2978,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>476</v>
@@ -2971,13 +2992,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>476</v>
@@ -2985,10 +3006,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>473</v>
@@ -2996,10 +3017,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>473</v>
@@ -3007,10 +3028,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>473</v>
@@ -3018,13 +3039,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>476</v>
@@ -5235,6 +5256,35 @@
       <c r="G10" s="3" t="s">
         <v>566</v>
       </c>
+      <c r="H10" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>573</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5254,19 +5304,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>517</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>461</v>
@@ -5277,157 +5327,157 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>553</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>551</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>

--- a/GRADO_CLAUDE.xlsx
+++ b/GRADO_CLAUDE.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="643">
   <si>
     <t>id_titulo</t>
   </si>
@@ -58,7 +58,7 @@
     <t>TIT0002</t>
   </si>
   <si>
-    <t>Caballero y Gran Cruz de la Orden de Carlos III</t>
+    <t>Gran Cruz de la Orden de Carlos III</t>
   </si>
   <si>
     <t>Real Orden de Carlos III</t>
@@ -193,7 +193,7 @@
     <t>TIT0013</t>
   </si>
   <si>
-    <t>Caballero y Cruz de la Orden de Carlos III</t>
+    <t>Cruz de la Orden de Carlos III</t>
   </si>
   <si>
     <t>TIT0014</t>
@@ -385,6 +385,9 @@
     <t>orden</t>
   </si>
   <si>
+    <t>id_nacion</t>
+  </si>
+  <si>
     <t>rama</t>
   </si>
   <si>
@@ -469,6 +472,18 @@
     <t>Capitán general</t>
   </si>
   <si>
+    <t>GR13</t>
+  </si>
+  <si>
+    <t>Almirante de la Flota</t>
+  </si>
+  <si>
+    <t>NACI00002</t>
+  </si>
+  <si>
+    <t>Royal Navy</t>
+  </si>
+  <si>
     <t>id_funcion</t>
   </si>
   <si>
@@ -1399,6 +1414,9 @@
     <t>Junta de Temporalidades de Lima</t>
   </si>
   <si>
+    <t>JEF057</t>
+  </si>
+  <si>
     <t>id_comision</t>
   </si>
   <si>
@@ -1573,6 +1591,12 @@
     <t>Civil</t>
   </si>
   <si>
+    <t>RAM0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naval </t>
+  </si>
+  <si>
     <t>id_escuadra</t>
   </si>
   <si>
@@ -1582,9 +1606,6 @@
     <t>id_buque_insignia</t>
   </si>
   <si>
-    <t>id_nacion</t>
-  </si>
-  <si>
     <t>fecha_constitucion</t>
   </si>
   <si>
@@ -1744,6 +1765,24 @@
     <t>Bombardeo de castigo contra el corso argelino</t>
   </si>
   <si>
+    <t>ESC0011</t>
+  </si>
+  <si>
+    <t>Escuadra de convoy a Manila</t>
+  </si>
+  <si>
+    <t>Escuadra en convoy en travesía a Manila</t>
+  </si>
+  <si>
+    <t>ESC0012</t>
+  </si>
+  <si>
+    <t>Escuadra del Almirante Rodney</t>
+  </si>
+  <si>
+    <t>BUQ00224</t>
+  </si>
+  <si>
     <t>id_division</t>
   </si>
   <si>
@@ -1826,6 +1865,27 @@
   </si>
   <si>
     <t>2º Cuerpo de Batidores</t>
+  </si>
+  <si>
+    <t>DIVI00000011</t>
+  </si>
+  <si>
+    <t>División Cañoneras</t>
+  </si>
+  <si>
+    <t>PER00802</t>
+  </si>
+  <si>
+    <t>DIVI00000012</t>
+  </si>
+  <si>
+    <t>División Bergantines</t>
+  </si>
+  <si>
+    <t>BUQ00158</t>
+  </si>
+  <si>
+    <t>PER00516</t>
   </si>
   <si>
     <t>id_reales_ejercitos</t>
@@ -1899,7 +1959,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1933,6 +1993,10 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1962,7 +2026,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1977,6 +2041,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -2000,6 +2067,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2936,119 +3006,119 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -3064,7 +3134,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="16.38"/>
-    <col customWidth="1" min="5" max="5" width="14.25"/>
+    <col customWidth="1" min="6" max="6" width="14.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3077,209 +3147,235 @@
       <c r="C1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>121</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>122</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="7">
+      <c r="B2" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="8">
         <v>1.0</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E2" s="5"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C3" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="7">
+      <c r="B4" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="8">
         <v>3.0</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="7">
+      <c r="B5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="8">
         <v>4.0</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="5"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="7">
+      <c r="B6" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="8">
         <v>5.0</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="7">
+      <c r="B7" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="8">
         <v>6.0</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C8" s="7">
+      <c r="B8" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="8">
         <v>7.0</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="5"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="7">
+      <c r="B9" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="8">
         <v>8.0</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>140</v>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="7">
+      <c r="B10" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="8">
         <v>9.0</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="5"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="7">
+      <c r="B11" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="8">
         <v>10.0</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" s="5"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="6"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="7">
+      <c r="B12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="8">
         <v>11.0</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="C13" s="7">
+      <c r="B13" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="8">
         <v>12.0</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="5"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="6"/>
     </row>
     <row r="14">
-      <c r="A14" s="5"/>
+      <c r="A14" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5"/>
+      <c r="A15" s="6"/>
     </row>
     <row r="16">
-      <c r="A16" s="5"/>
+      <c r="A16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="5"/>
+      <c r="A17" s="6"/>
     </row>
     <row r="18">
-      <c r="A18" s="5"/>
+      <c r="A18" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -3299,620 +3395,620 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>154</v>
+      <c r="A2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>157</v>
+      <c r="A3" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>160</v>
+      <c r="A4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>165</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>158</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>164</v>
+      <c r="A6" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>166</v>
+      <c r="A7" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>168</v>
+      <c r="A8" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>170</v>
+      <c r="A9" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>172</v>
+      <c r="A10" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>174</v>
+      <c r="A11" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>176</v>
+      <c r="A12" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>178</v>
+      <c r="A13" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>180</v>
+      <c r="A14" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>182</v>
+      <c r="A15" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>184</v>
+      <c r="A16" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>187</v>
+      <c r="A17" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>189</v>
+      <c r="A18" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>190</v>
+      <c r="A19" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>192</v>
+      <c r="A20" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>195</v>
+      <c r="A21" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>196</v>
+      <c r="A22" s="9" t="s">
+        <v>201</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
-        <v>198</v>
+      <c r="A23" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>200</v>
+      <c r="A24" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>202</v>
+      <c r="A25" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>204</v>
+      <c r="A26" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>206</v>
+      <c r="A27" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>208</v>
+      <c r="A28" s="9" t="s">
+        <v>213</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="s">
-        <v>210</v>
+      <c r="A29" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>212</v>
+      <c r="A30" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="s">
-        <v>214</v>
+      <c r="A31" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>216</v>
+      <c r="A32" s="9" t="s">
+        <v>221</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>218</v>
+      <c r="A33" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="s">
-        <v>220</v>
+      <c r="A34" s="9" t="s">
+        <v>225</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="s">
-        <v>222</v>
+      <c r="A35" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="s">
-        <v>224</v>
+      <c r="A36" s="9" t="s">
+        <v>229</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="s">
-        <v>226</v>
+      <c r="A37" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="s">
-        <v>228</v>
+      <c r="A38" s="9" t="s">
+        <v>233</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="s">
-        <v>230</v>
+      <c r="A39" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="s">
-        <v>232</v>
+      <c r="A40" s="9" t="s">
+        <v>237</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="s">
-        <v>234</v>
+      <c r="A41" s="9" t="s">
+        <v>239</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="s">
-        <v>236</v>
+      <c r="A42" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="s">
-        <v>238</v>
+      <c r="A43" s="9" t="s">
+        <v>243</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="s">
-        <v>240</v>
+      <c r="A44" s="9" t="s">
+        <v>245</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="s">
-        <v>242</v>
+      <c r="A45" s="9" t="s">
+        <v>247</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="s">
-        <v>244</v>
+      <c r="A46" s="9" t="s">
+        <v>249</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="s">
-        <v>246</v>
+      <c r="A47" s="9" t="s">
+        <v>251</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="s">
-        <v>248</v>
+      <c r="A48" s="9" t="s">
+        <v>253</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="s">
-        <v>250</v>
+      <c r="A49" s="9" t="s">
+        <v>255</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="s">
-        <v>252</v>
+      <c r="A50" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="s">
-        <v>254</v>
+      <c r="A51" s="9" t="s">
+        <v>259</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="s">
-        <v>256</v>
+      <c r="A52" s="9" t="s">
+        <v>261</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="s">
-        <v>258</v>
+      <c r="A53" s="9" t="s">
+        <v>263</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="s">
-        <v>260</v>
+      <c r="A54" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="s">
-        <v>262</v>
+      <c r="A55" s="9" t="s">
+        <v>267</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="s">
-        <v>264</v>
+      <c r="A56" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="s">
-        <v>266</v>
+      <c r="A57" s="9" t="s">
+        <v>271</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="s">
-        <v>268</v>
+      <c r="A58" s="9" t="s">
+        <v>273</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="s">
-        <v>270</v>
+      <c r="A59" s="9" t="s">
+        <v>275</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="s">
-        <v>272</v>
+      <c r="A60" s="9" t="s">
+        <v>277</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="s">
-        <v>274</v>
+      <c r="A61" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="8" t="s">
-        <v>276</v>
+      <c r="A62" s="9" t="s">
+        <v>281</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="s">
-        <v>278</v>
+      <c r="A63" s="9" t="s">
+        <v>283</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="s">
-        <v>280</v>
+      <c r="A64" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="8" t="s">
-        <v>282</v>
+      <c r="A65" s="9" t="s">
+        <v>287</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="s">
-        <v>284</v>
+      <c r="A66" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="8" t="s">
-        <v>286</v>
+      <c r="A67" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="s">
-        <v>288</v>
+      <c r="A68" s="9" t="s">
+        <v>293</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="s">
-        <v>290</v>
+      <c r="A69" s="9" t="s">
+        <v>295</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="s">
-        <v>292</v>
+      <c r="A70" s="9" t="s">
+        <v>297</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="s">
-        <v>294</v>
+      <c r="A71" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="s">
-        <v>296</v>
+      <c r="A72" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="s">
-        <v>298</v>
+      <c r="A73" s="9" t="s">
+        <v>303</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="s">
-        <v>300</v>
+      <c r="A74" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="s">
-        <v>302</v>
+      <c r="A75" s="9" t="s">
+        <v>307</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3932,10 +4028,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>120</v>
@@ -3943,160 +4039,160 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C2" s="9">
+        <v>311</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="10">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C3" s="9">
+        <v>313</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" s="10">
         <v>2.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C4" s="9">
+        <v>316</v>
+      </c>
+      <c r="C4" s="10">
         <v>3.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C5" s="9">
+        <v>318</v>
+      </c>
+      <c r="C5" s="10">
         <v>4.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="9">
+        <v>319</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="10">
         <v>5.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="9">
+        <v>320</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" s="10">
         <v>6.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="9">
+        <v>322</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="10">
         <v>7.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="9">
+        <v>324</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C9" s="10">
         <v>8.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="9">
+        <v>326</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="10">
         <v>9.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="9">
+        <v>328</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" s="10">
         <v>10.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="C12" s="9">
+        <v>330</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C12" s="10">
         <v>11.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C13" s="9">
+        <v>332</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" s="10">
         <v>12.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="C14" s="9">
+        <v>334</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C14" s="10">
         <v>13.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C15" s="9">
+        <v>336</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="10">
         <v>14.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="9"/>
+      <c r="C16" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4115,660 +4211,668 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>336</v>
+      <c r="A1" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>343</v>
+      <c r="D3" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>351</v>
+      <c r="D6" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>343</v>
+        <v>349</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>343</v>
+        <v>349</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>343</v>
+        <v>349</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>367</v>
+        <v>371</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>340</v>
+        <v>346</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>379</v>
+        <v>386</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>340</v>
+        <v>392</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>376</v>
+        <v>391</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>340</v>
+        <v>396</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>394</v>
+        <v>344</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>394</v>
+        <v>400</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>343</v>
+        <v>408</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>340</v>
+        <v>413</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>340</v>
+        <v>418</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>417</v>
+        <v>342</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>422</v>
+        <v>344</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>422</v>
+        <v>425</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -4789,42 +4893,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -4844,76 +4948,76 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>44</v>
@@ -4921,109 +5025,120 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -5047,243 +5162,277 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>520</v>
+        <v>121</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>550</v>
+        <v>534</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1775.0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1777.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -5304,180 +5453,223 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>580</v>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>
